--- a/saidas/historico_runs/historico_runs_2026_08_07.xlsx
+++ b/saidas/historico_runs/historico_runs_2026_08_07.xlsx
@@ -4923,7 +4923,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -4932,25 +4932,25 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I73" t="n">
-        <v>0.47</v>
+        <v>0.229</v>
       </c>
       <c r="J73" t="n">
-        <v>0.711</v>
+        <v>0.718</v>
       </c>
       <c r="K73" t="n">
-        <v>0.258</v>
+        <v>0.339</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -4962,14 +4962,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R73" t="n">
-        <v>0.531</v>
+        <v>0.514</v>
       </c>
     </row>
   </sheetData>
@@ -4983,7 +4983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O503"/>
+  <dimension ref="A1:O506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35317,12 +35317,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -35331,13 +35331,13 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>0.2985</v>
+        <v>0.4989</v>
       </c>
       <c r="F502" t="n">
-        <v>1.095515</v>
+        <v>1.107236</v>
       </c>
       <c r="G502" t="n">
-        <v>1.0613</v>
+        <v>0.8064</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
@@ -35350,28 +35350,28 @@
         </is>
       </c>
       <c r="J502" t="n">
-        <v>0.5405</v>
+        <v>0.482</v>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>RV_RANK</t>
         </is>
       </c>
       <c r="L502" t="n">
-        <v>0.5405</v>
+        <v>0.482</v>
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
         </is>
       </c>
       <c r="N502" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="O502" t="n">
-        <v>0.2293</v>
+        <v>0.6346000000000001</v>
       </c>
     </row>
     <row r="503">
@@ -35380,61 +35380,250 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
+          <t>BBDC4</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="F503" t="n">
+        <v>1.144711</v>
+      </c>
+      <c r="G503" t="n">
+        <v>1.8258</v>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>alerta_executor_nivel_B</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="J503" t="n">
+        <v>0.6088</v>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="L503" t="n">
+        <v>0.6088</v>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="O503" t="n">
+        <v>0.2293</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="F504" t="n">
+        <v>1.073351</v>
+      </c>
+      <c r="G504" t="n">
+        <v>0.8647</v>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>alerta_executor_nivel_B</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="J504" t="n">
+        <v>0.5022</v>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>RV_RANK</t>
+        </is>
+      </c>
+      <c r="L504" t="n">
+        <v>0.5022</v>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="O504" t="n">
+        <v>0.1379</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
           <t>BHIA3</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr">
+      <c r="C505" t="inlineStr">
         <is>
           <t>Alerta PUT</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr">
+      <c r="D505" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E503" t="n">
-        <v>0.2165</v>
-      </c>
-      <c r="F503" t="n">
-        <v>1.122074</v>
-      </c>
-      <c r="G503" t="n">
-        <v>1.1522</v>
-      </c>
-      <c r="H503" t="inlineStr">
+      <c r="E505" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="F505" t="n">
+        <v>1.087637</v>
+      </c>
+      <c r="G505" t="n">
+        <v>1.4099</v>
+      </c>
+      <c r="H505" t="inlineStr">
         <is>
           <t>alerta_executor_nivel_B</t>
         </is>
       </c>
-      <c r="I503" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="J503" t="n">
-        <v>0.5489000000000001</v>
-      </c>
-      <c r="K503" t="inlineStr">
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="J505" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="K505" t="inlineStr">
         <is>
           <t>RV_RANK</t>
         </is>
       </c>
-      <c r="L503" t="n">
-        <v>0.5489000000000001</v>
-      </c>
-      <c r="M503" t="inlineStr">
+      <c r="L505" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="M505" t="inlineStr">
         <is>
           <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
         </is>
       </c>
-      <c r="N503" t="inlineStr">
+      <c r="N505" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="O503" t="n">
-        <v>0.7107</v>
+      <c r="O505" t="n">
+        <v>0.7175</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>SBFG3</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="F506" t="n">
+        <v>1.388515</v>
+      </c>
+      <c r="G506" t="n">
+        <v>0.8218</v>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>alerta_executor_nivel_B</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="J506" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="L506" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="O506" t="n">
+        <v>0.0607</v>
       </c>
     </row>
   </sheetData>
@@ -35576,13 +35765,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46197</v>
+        <v>46241</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -35590,10 +35779,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="6">
@@ -35929,10 +36118,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.679</v>
+        <v>0.68</v>
       </c>
       <c r="G18" t="n">
-        <v>0.711</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="19">
@@ -36111,52 +36300,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FLRY3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46159</v>
+        <v>46173</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46181</v>
+        <v>46241</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>Alerta CALL, Alerta PUT</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.648</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>FLRY3</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46173</v>
+        <v>46159</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46239</v>
+        <v>46181</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alerta CALL, Alerta PUT</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.648</v>
-      </c>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -36380,55 +36569,55 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HAPV3</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46195</v>
+        <v>46154</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46197</v>
+        <v>46241</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL, Alerta PUT</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.235</v>
+        <v>0.063</v>
       </c>
       <c r="G37" t="n">
-        <v>1.235</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>HAPV3</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46163</v>
+        <v>46195</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46227</v>
+        <v>46197</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Alerta PUT, Monitorar CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.164</v>
+        <v>1.235</v>
       </c>
       <c r="G38" t="n">
-        <v>0.164</v>
+        <v>1.235</v>
       </c>
     </row>
     <row r="39">
@@ -36457,79 +36646,79 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENGI11</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>3</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46200</v>
+        <v>46163</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46202</v>
+        <v>46227</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT, Monitorar CALL</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.054</v>
+        <v>0.164</v>
       </c>
       <c r="G40" t="n">
-        <v>0.054</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46153</v>
+        <v>46200</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46154</v>
+        <v>46202</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>Alerta CALL</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.054</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOAU4</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46238</v>
+        <v>46153</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46239</v>
+        <v>46154</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.191</v>
-      </c>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -36588,28 +36777,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46154</v>
+        <v>46210</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46228</v>
+        <v>46211</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Alerta CALL, Alerta PUT</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.065</v>
+        <v>0.385</v>
       </c>
       <c r="G45" t="n">
-        <v>0.065</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="46">
@@ -36642,28 +36831,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46210</v>
+        <v>46238</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46211</v>
+        <v>46239</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.385</v>
+        <v>0.191</v>
       </c>
       <c r="G47" t="n">
-        <v>0.385</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="48">
